--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -54,73 +54,76 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-07-29T09:46:30+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>用於記錄勞工之嚼檳榔習慣與量化資料。本 Profile 基於 Observation 資源，採用與臺灣癌症登記短表實作指引 (TWCR_SF) 相同之元件架構及值集，以便進行跨系統之整合介接。</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
     <t>false</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-07-26T18:45:10+08:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>用於記錄勞工之嚼檳榔習慣與量化資料。本 Profile 基於 Observation 資源，採用與臺灣癌症登記短表實作指引 (TWCR_SF) 相同之元件架構及值集，以便進行跨系統之整合介接。</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>resource</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Observation</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
-  </si>
-  <si>
-    <t>Abstract</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1864,15 +1867,15 @@
         <v>35</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1885,17 +1888,17 @@
   <dimension ref="A1:AP78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.8671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.76171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1904,156 +1907,156 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.58203125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.87109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
@@ -2065,14 +2068,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>22</v>
@@ -2084,16 +2087,16 @@
         <v>22</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2146,28 +2149,28 @@
         <v>32</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>22</v>
@@ -2178,10 +2181,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2189,10 +2192,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>22</v>
@@ -2201,19 +2204,19 @@
         <v>22</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2263,13 +2266,13 @@
         <v>22</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>22</v>
@@ -2298,10 +2301,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2309,10 +2312,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>22</v>
@@ -2321,16 +2324,16 @@
         <v>22</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2381,19 +2384,19 @@
         <v>22</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>22</v>
@@ -2416,10 +2419,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2427,31 +2430,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2501,19 +2504,19 @@
         <v>22</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>22</v>
@@ -2536,10 +2539,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2547,10 +2550,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>22</v>
@@ -2562,16 +2565,16 @@
         <v>22</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2597,13 +2600,13 @@
         <v>22</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>22</v>
@@ -2621,19 +2624,19 @@
         <v>22</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>22</v>
@@ -2656,21 +2659,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>22</v>
@@ -2682,16 +2685,16 @@
         <v>22</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2741,19 +2744,19 @@
         <v>22</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>22</v>
@@ -2765,7 +2768,7 @@
         <v>22</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>22</v>
@@ -2776,21 +2779,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>22</v>
@@ -2802,16 +2805,16 @@
         <v>22</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2861,13 +2864,13 @@
         <v>22</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>22</v>
@@ -2885,7 +2888,7 @@
         <v>22</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>22</v>
@@ -2896,21 +2899,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>22</v>
@@ -2922,16 +2925,16 @@
         <v>22</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2981,19 +2984,19 @@
         <v>22</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>22</v>
@@ -3005,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>22</v>
@@ -3016,45 +3019,45 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>22</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>22</v>
@@ -3103,19 +3106,19 @@
         <v>22</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>22</v>
@@ -3127,7 +3130,7 @@
         <v>22</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>22</v>
@@ -3138,10 +3141,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3149,10 +3152,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>22</v>
@@ -3161,20 +3164,20 @@
         <v>22</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>22</v>
@@ -3223,34 +3226,34 @@
         <v>22</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>22</v>
@@ -3258,21 +3261,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>22</v>
@@ -3281,20 +3284,20 @@
         <v>22</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>22</v>
@@ -3343,31 +3346,31 @@
         <v>22</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>22</v>
@@ -3378,21 +3381,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>22</v>
@@ -3401,19 +3404,19 @@
         <v>22</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3463,31 +3466,31 @@
         <v>22</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>22</v>
@@ -3498,10 +3501,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3509,34 +3512,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>22</v>
@@ -3546,7 +3549,7 @@
         <v>22</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>22</v>
@@ -3561,13 +3564,13 @@
         <v>22</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>22</v>
@@ -3585,34 +3588,34 @@
         <v>22</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>22</v>
@@ -3620,10 +3623,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3631,10 +3634,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>22</v>
@@ -3646,19 +3649,19 @@
         <v>22</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>22</v>
@@ -3668,7 +3671,7 @@
         <v>22</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>22</v>
@@ -3683,13 +3686,13 @@
         <v>22</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>22</v>
@@ -3707,19 +3710,19 @@
         <v>22</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>22</v>
@@ -3731,10 +3734,10 @@
         <v>22</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>22</v>
@@ -3742,21 +3745,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>22</v>
@@ -3765,22 +3768,22 @@
         <v>22</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>22</v>
@@ -3790,7 +3793,7 @@
         <v>22</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>22</v>
@@ -3805,13 +3808,13 @@
         <v>22</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>22</v>
@@ -3829,45 +3832,45 @@
         <v>22</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3875,10 +3878,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>22</v>
@@ -3887,22 +3890,22 @@
         <v>22</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>22</v>
@@ -3951,34 +3954,34 @@
         <v>22</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>22</v>
@@ -3986,10 +3989,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3997,10 +4000,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>22</v>
@@ -4009,19 +4012,19 @@
         <v>22</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4071,34 +4074,34 @@
         <v>22</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>22</v>
@@ -4106,21 +4109,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>22</v>
@@ -4129,22 +4132,22 @@
         <v>22</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>22</v>
@@ -4193,34 +4196,34 @@
         <v>22</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>22</v>
@@ -4228,21 +4231,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>22</v>
@@ -4251,22 +4254,22 @@
         <v>22</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>22</v>
@@ -4315,34 +4318,34 @@
         <v>22</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>22</v>
@@ -4350,10 +4353,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4361,10 +4364,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>22</v>
@@ -4373,19 +4376,19 @@
         <v>22</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4435,19 +4438,19 @@
         <v>22</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>22</v>
@@ -4456,13 +4459,13 @@
         <v>22</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>22</v>
@@ -4470,10 +4473,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4481,10 +4484,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>22</v>
@@ -4493,20 +4496,20 @@
         <v>22</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>22</v>
@@ -4555,34 +4558,34 @@
         <v>22</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>22</v>
@@ -4590,10 +4593,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4601,10 +4604,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>22</v>
@@ -4613,22 +4616,22 @@
         <v>22</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>22</v>
@@ -4677,45 +4680,45 @@
         <v>22</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4723,10 +4726,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>22</v>
@@ -4738,19 +4741,19 @@
         <v>22</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>22</v>
@@ -4775,13 +4778,13 @@
         <v>22</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>22</v>
@@ -4799,19 +4802,19 @@
         <v>22</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>22</v>
@@ -4820,10 +4823,10 @@
         <v>22</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>22</v>
@@ -4834,21 +4837,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>22</v>
@@ -4860,19 +4863,19 @@
         <v>22</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>22</v>
@@ -4897,13 +4900,13 @@
         <v>22</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>22</v>
@@ -4921,45 +4924,45 @@
         <v>22</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4967,10 +4970,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>22</v>
@@ -4982,19 +4985,19 @@
         <v>22</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>22</v>
@@ -5043,19 +5046,19 @@
         <v>22</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>22</v>
@@ -5064,10 +5067,10 @@
         <v>22</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>22</v>
@@ -5078,10 +5081,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5089,10 +5092,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>22</v>
@@ -5104,16 +5107,16 @@
         <v>22</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5139,13 +5142,13 @@
         <v>22</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>22</v>
@@ -5163,45 +5166,45 @@
         <v>22</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5209,10 +5212,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>22</v>
@@ -5224,19 +5227,19 @@
         <v>22</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>22</v>
@@ -5261,13 +5264,13 @@
         <v>22</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>22</v>
@@ -5285,19 +5288,19 @@
         <v>22</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>22</v>
@@ -5306,10 +5309,10 @@
         <v>22</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>22</v>
@@ -5320,10 +5323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5331,10 +5334,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>22</v>
@@ -5346,16 +5349,16 @@
         <v>22</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5405,45 +5408,45 @@
         <v>22</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5451,10 +5454,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>22</v>
@@ -5466,16 +5469,16 @@
         <v>22</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5525,45 +5528,45 @@
         <v>22</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5571,10 +5574,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>22</v>
@@ -5586,19 +5589,19 @@
         <v>22</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>22</v>
@@ -5647,19 +5650,19 @@
         <v>22</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>22</v>
@@ -5668,10 +5671,10 @@
         <v>22</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>22</v>
@@ -5682,10 +5685,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5693,10 +5696,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>22</v>
@@ -5708,13 +5711,13 @@
         <v>22</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5765,13 +5768,13 @@
         <v>22</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>22</v>
@@ -5789,7 +5792,7 @@
         <v>22</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>22</v>
@@ -5800,21 +5803,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>22</v>
@@ -5826,16 +5829,16 @@
         <v>22</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5885,19 +5888,19 @@
         <v>22</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>22</v>
@@ -5909,7 +5912,7 @@
         <v>22</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>22</v>
@@ -5920,45 +5923,45 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>22</v>
@@ -6007,19 +6010,19 @@
         <v>22</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>22</v>
@@ -6031,7 +6034,7 @@
         <v>22</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>22</v>
@@ -6042,10 +6045,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6053,10 +6056,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>22</v>
@@ -6068,13 +6071,13 @@
         <v>22</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6125,19 +6128,19 @@
         <v>22</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>22</v>
@@ -6146,10 +6149,10 @@
         <v>22</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>22</v>
@@ -6160,10 +6163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6171,10 +6174,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>22</v>
@@ -6186,13 +6189,13 @@
         <v>22</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6243,19 +6246,19 @@
         <v>22</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>22</v>
@@ -6264,10 +6267,10 @@
         <v>22</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>22</v>
@@ -6278,10 +6281,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6289,10 +6292,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>22</v>
@@ -6304,19 +6307,19 @@
         <v>22</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>22</v>
@@ -6341,13 +6344,13 @@
         <v>22</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>22</v>
@@ -6365,31 +6368,31 @@
         <v>22</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>22</v>
@@ -6400,10 +6403,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6411,10 +6414,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>22</v>
@@ -6426,19 +6429,19 @@
         <v>22</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>22</v>
@@ -6463,13 +6466,13 @@
         <v>22</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>22</v>
@@ -6487,31 +6490,31 @@
         <v>22</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>22</v>
@@ -6522,10 +6525,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6533,10 +6536,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>22</v>
@@ -6548,17 +6551,17 @@
         <v>22</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>22</v>
@@ -6607,19 +6610,19 @@
         <v>22</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>22</v>
@@ -6631,7 +6634,7 @@
         <v>22</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>22</v>
@@ -6642,10 +6645,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6653,10 +6656,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>22</v>
@@ -6668,13 +6671,13 @@
         <v>22</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6725,19 +6728,19 @@
         <v>22</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>22</v>
@@ -6746,10 +6749,10 @@
         <v>22</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>22</v>
@@ -6760,10 +6763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6771,10 +6774,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>22</v>
@@ -6783,19 +6786,19 @@
         <v>22</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6845,19 +6848,19 @@
         <v>22</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>22</v>
@@ -6866,10 +6869,10 @@
         <v>22</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>22</v>
@@ -6880,10 +6883,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6891,10 +6894,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>22</v>
@@ -6903,19 +6906,19 @@
         <v>22</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6965,19 +6968,19 @@
         <v>22</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>22</v>
@@ -6986,10 +6989,10 @@
         <v>22</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>22</v>
@@ -7000,10 +7003,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7011,10 +7014,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>22</v>
@@ -7023,22 +7026,22 @@
         <v>22</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>22</v>
@@ -7075,29 +7078,29 @@
         <v>22</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>22</v>
@@ -7106,10 +7109,10 @@
         <v>22</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>22</v>
@@ -7120,10 +7123,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7131,10 +7134,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>22</v>
@@ -7146,13 +7149,13 @@
         <v>22</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7203,13 +7206,13 @@
         <v>22</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>22</v>
@@ -7227,7 +7230,7 @@
         <v>22</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>22</v>
@@ -7238,21 +7241,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>22</v>
@@ -7264,16 +7267,16 @@
         <v>22</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7323,19 +7326,19 @@
         <v>22</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>22</v>
@@ -7347,7 +7350,7 @@
         <v>22</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>22</v>
@@ -7358,45 +7361,45 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>22</v>
@@ -7445,19 +7448,19 @@
         <v>22</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>22</v>
@@ -7469,7 +7472,7 @@
         <v>22</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>22</v>
@@ -7480,10 +7483,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7491,10 +7494,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>22</v>
@@ -7503,22 +7506,22 @@
         <v>22</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>22</v>
@@ -7543,13 +7546,13 @@
         <v>22</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>22</v>
@@ -7567,34 +7570,34 @@
         <v>22</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>22</v>
@@ -7602,10 +7605,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7613,10 +7616,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>22</v>
@@ -7625,22 +7628,22 @@
         <v>22</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>22</v>
@@ -7689,45 +7692,45 @@
         <v>22</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7735,10 +7738,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>22</v>
@@ -7750,19 +7753,19 @@
         <v>22</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>22</v>
@@ -7787,13 +7790,13 @@
         <v>22</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>22</v>
@@ -7811,19 +7814,19 @@
         <v>22</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>22</v>
@@ -7832,10 +7835,10 @@
         <v>22</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>22</v>
@@ -7846,21 +7849,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>22</v>
@@ -7872,19 +7875,19 @@
         <v>22</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>22</v>
@@ -7909,13 +7912,13 @@
         <v>22</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>22</v>
@@ -7933,45 +7936,45 @@
         <v>22</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7979,10 +7982,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>22</v>
@@ -7994,19 +7997,19 @@
         <v>22</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>22</v>
@@ -8055,19 +8058,19 @@
         <v>22</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>22</v>
@@ -8076,10 +8079,10 @@
         <v>22</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>22</v>
@@ -8090,23 +8093,23 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>22</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>22</v>
@@ -8115,22 +8118,22 @@
         <v>22</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>22</v>
@@ -8179,19 +8182,19 @@
         <v>22</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>22</v>
@@ -8200,10 +8203,10 @@
         <v>22</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>22</v>
@@ -8214,10 +8217,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8225,10 +8228,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>22</v>
@@ -8240,13 +8243,13 @@
         <v>22</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8297,13 +8300,13 @@
         <v>22</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>22</v>
@@ -8321,7 +8324,7 @@
         <v>22</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>22</v>
@@ -8332,21 +8335,21 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>22</v>
@@ -8358,16 +8361,16 @@
         <v>22</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8417,19 +8420,19 @@
         <v>22</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>22</v>
@@ -8441,7 +8444,7 @@
         <v>22</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>22</v>
@@ -8452,45 +8455,45 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>22</v>
@@ -8539,19 +8542,19 @@
         <v>22</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>22</v>
@@ -8563,7 +8566,7 @@
         <v>22</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>22</v>
@@ -8574,10 +8577,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8585,10 +8588,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>22</v>
@@ -8597,22 +8600,22 @@
         <v>22</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>22</v>
@@ -8622,7 +8625,7 @@
         <v>22</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>22</v>
@@ -8637,13 +8640,13 @@
         <v>22</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>22</v>
@@ -8661,34 +8664,34 @@
         <v>22</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>22</v>
@@ -8696,10 +8699,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8707,10 +8710,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>22</v>
@@ -8719,22 +8722,22 @@
         <v>22</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>22</v>
@@ -8759,11 +8762,11 @@
         <v>22</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>22</v>
@@ -8781,45 +8784,45 @@
         <v>22</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8827,10 +8830,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>22</v>
@@ -8842,19 +8845,19 @@
         <v>22</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>22</v>
@@ -8879,13 +8882,13 @@
         <v>22</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>22</v>
@@ -8903,19 +8906,19 @@
         <v>22</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>22</v>
@@ -8924,10 +8927,10 @@
         <v>22</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>22</v>
@@ -8938,21 +8941,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>22</v>
@@ -8964,19 +8967,19 @@
         <v>22</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>22</v>
@@ -9001,13 +9004,13 @@
         <v>22</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>22</v>
@@ -9025,45 +9028,45 @@
         <v>22</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9071,10 +9074,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>22</v>
@@ -9086,19 +9089,19 @@
         <v>22</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>22</v>
@@ -9147,19 +9150,19 @@
         <v>22</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>22</v>
@@ -9168,10 +9171,10 @@
         <v>22</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>22</v>
@@ -9182,23 +9185,23 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>22</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>22</v>
@@ -9207,22 +9210,22 @@
         <v>22</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>22</v>
@@ -9271,19 +9274,19 @@
         <v>22</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>22</v>
@@ -9292,10 +9295,10 @@
         <v>22</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>22</v>
@@ -9306,10 +9309,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9317,10 +9320,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>22</v>
@@ -9332,13 +9335,13 @@
         <v>22</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9389,13 +9392,13 @@
         <v>22</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>22</v>
@@ -9413,7 +9416,7 @@
         <v>22</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>22</v>
@@ -9424,21 +9427,21 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>22</v>
@@ -9450,16 +9453,16 @@
         <v>22</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9509,19 +9512,19 @@
         <v>22</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>22</v>
@@ -9533,7 +9536,7 @@
         <v>22</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>22</v>
@@ -9544,45 +9547,45 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>22</v>
@@ -9631,19 +9634,19 @@
         <v>22</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>22</v>
@@ -9655,7 +9658,7 @@
         <v>22</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>22</v>
@@ -9666,10 +9669,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9677,10 +9680,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>22</v>
@@ -9689,22 +9692,22 @@
         <v>22</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>22</v>
@@ -9714,7 +9717,7 @@
         <v>22</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>22</v>
@@ -9729,13 +9732,13 @@
         <v>22</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>22</v>
@@ -9753,34 +9756,34 @@
         <v>22</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>22</v>
@@ -9788,10 +9791,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9799,10 +9802,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>22</v>
@@ -9811,22 +9814,22 @@
         <v>22</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>22</v>
@@ -9851,11 +9854,11 @@
         <v>22</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>22</v>
@@ -9873,45 +9876,45 @@
         <v>22</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9919,10 +9922,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>22</v>
@@ -9934,19 +9937,19 @@
         <v>22</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>22</v>
@@ -9971,13 +9974,13 @@
         <v>22</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>22</v>
@@ -9995,19 +9998,19 @@
         <v>22</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>22</v>
@@ -10016,10 +10019,10 @@
         <v>22</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>22</v>
@@ -10030,21 +10033,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>22</v>
@@ -10056,19 +10059,19 @@
         <v>22</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>22</v>
@@ -10093,13 +10096,13 @@
         <v>22</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>22</v>
@@ -10117,45 +10120,45 @@
         <v>22</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10163,10 +10166,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>22</v>
@@ -10178,19 +10181,19 @@
         <v>22</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>22</v>
@@ -10239,19 +10242,19 @@
         <v>22</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>22</v>
@@ -10260,10 +10263,10 @@
         <v>22</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>22</v>
@@ -10274,23 +10277,23 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>22</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>22</v>
@@ -10299,22 +10302,22 @@
         <v>22</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>22</v>
@@ -10363,19 +10366,19 @@
         <v>22</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>22</v>
@@ -10384,10 +10387,10 @@
         <v>22</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>22</v>
@@ -10398,10 +10401,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10409,10 +10412,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>22</v>
@@ -10424,13 +10427,13 @@
         <v>22</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10481,13 +10484,13 @@
         <v>22</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>22</v>
@@ -10505,7 +10508,7 @@
         <v>22</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>22</v>
@@ -10516,21 +10519,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -10542,16 +10545,16 @@
         <v>22</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10601,19 +10604,19 @@
         <v>22</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>22</v>
@@ -10625,7 +10628,7 @@
         <v>22</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>22</v>
@@ -10636,45 +10639,45 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>22</v>
@@ -10723,19 +10726,19 @@
         <v>22</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>22</v>
@@ -10747,7 +10750,7 @@
         <v>22</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>22</v>
@@ -10758,10 +10761,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10769,10 +10772,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>22</v>
@@ -10781,22 +10784,22 @@
         <v>22</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>22</v>
@@ -10806,7 +10809,7 @@
         <v>22</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>22</v>
@@ -10821,13 +10824,13 @@
         <v>22</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>22</v>
@@ -10845,34 +10848,34 @@
         <v>22</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>22</v>
@@ -10880,10 +10883,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10891,10 +10894,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>22</v>
@@ -10903,22 +10906,22 @@
         <v>22</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>22</v>
@@ -10943,11 +10946,11 @@
         <v>22</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>22</v>
@@ -10965,45 +10968,45 @@
         <v>22</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11011,10 +11014,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>22</v>
@@ -11026,19 +11029,19 @@
         <v>22</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>22</v>
@@ -11063,13 +11066,13 @@
         <v>22</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>22</v>
@@ -11087,19 +11090,19 @@
         <v>22</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>22</v>
@@ -11108,10 +11111,10 @@
         <v>22</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>22</v>
@@ -11122,21 +11125,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>22</v>
@@ -11148,19 +11151,19 @@
         <v>22</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>22</v>
@@ -11185,13 +11188,13 @@
         <v>22</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>22</v>
@@ -11209,45 +11212,45 @@
         <v>22</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11255,10 +11258,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -11270,19 +11273,19 @@
         <v>22</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>22</v>
@@ -11331,19 +11334,19 @@
         <v>22</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>22</v>
@@ -11352,10 +11355,10 @@
         <v>22</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>用於記錄勞工之嚼檳榔狀態與量化資料。狀態以 `value[x]` 承載（值集 VS-BetelNutStatus，與吸菸之 CS-SmokingStatus 逐碼對稱）；每日嚼食量、嚼食年數與戒除期間以 `component` 之 `Quantity` 承載（UCUM）。上游臺灣癌症登記短表 (TWCR_SF) 之級距碼降為可選 component（extensible），供與癌症登記勾稽。</t>
+    <t>【主管機關：國民健康署】用於記錄勞工之嚼檳榔狀態與量化資料。狀態以 `value[x]` 承載（值集 VS-BetelNutStatus，與吸菸之 CS-SmokingStatus 逐碼對稱）；每日嚼食量、嚼食年數與戒除期間以 `component` 之 `Quantity` 承載（UCUM）。上游臺灣癌症登記短表 (TWCR_SF) 之級距碼降為可選 component（extensible），供與癌症登記勾稽。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6285" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6284" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1680,7 +1680,7 @@
   &lt;coding&gt;
     &lt;system value="https://twcore.mohw.gov.tw/ig/twha/CodeSystem/CS-BetelNutComponent"/&gt;
     &lt;code value="duration-years"/&gt;
-    &lt;display value="嚼食年數"/&gt;
+    &lt;display value="嚼食持續期間"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1709,7 +1709,7 @@
     <t>Observation.component:durationYears.value[x].code</t>
   </si>
   <si>
-    <t>a</t>
+    <t>https://twcore.mohw.gov.tw/ig/twha/ValueSet/VS-TimeUnitYearMonth</t>
   </si>
   <si>
     <t>Observation.component:durationYears.dataAbsentReason</t>
@@ -1770,9 +1770,6 @@
   </si>
   <si>
     <t>Observation.component:cessationDuration.value[x].code</t>
-  </si>
-  <si>
-    <t>https://twcore.mohw.gov.tw/ig/twha/ValueSet/VS-TimeUnitYearMonth</t>
   </si>
   <si>
     <t>Observation.component:cessationDuration.dataAbsentReason</t>
@@ -12046,28 +12043,26 @@
         <v>22</v>
       </c>
       <c r="S80" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y80" s="2"/>
+      <c r="Z80" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>22</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>22</v>
@@ -14003,7 +13998,7 @@
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>22</v>
@@ -14056,7 +14051,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>447</v>
@@ -14178,7 +14173,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>451</v>
@@ -14300,7 +14295,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>452</v>
@@ -14422,13 +14417,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>22</v>
@@ -14546,7 +14541,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>434</v>
@@ -14664,7 +14659,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>435</v>
@@ -14784,7 +14779,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>436</v>
@@ -14906,7 +14901,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>437</v>
@@ -14954,7 +14949,7 @@
         <v>22</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>22</v>
@@ -15028,7 +15023,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>442</v>
@@ -15054,7 +15049,7 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>444</v>
@@ -15150,7 +15145,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>447</v>
@@ -15272,7 +15267,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>451</v>
@@ -15394,7 +15389,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>452</v>
@@ -15516,13 +15511,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>22</v>
@@ -15640,7 +15635,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>434</v>
@@ -15758,7 +15753,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>435</v>
@@ -15878,7 +15873,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>436</v>
@@ -16000,7 +15995,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>437</v>
@@ -16048,7 +16043,7 @@
         <v>22</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>22</v>
@@ -16122,7 +16117,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>442</v>
@@ -16148,7 +16143,7 @@
         <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>444</v>
@@ -16244,7 +16239,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>447</v>
@@ -16366,7 +16361,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>451</v>
@@ -16488,7 +16483,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>452</v>
@@ -16610,13 +16605,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>22</v>
@@ -16734,7 +16729,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>434</v>
@@ -16852,7 +16847,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>435</v>
@@ -16972,7 +16967,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>436</v>
@@ -17094,7 +17089,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>437</v>
@@ -17142,7 +17137,7 @@
         <v>22</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>22</v>
@@ -17216,7 +17211,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>442</v>
@@ -17283,7 +17278,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>22</v>
@@ -17336,7 +17331,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>447</v>
@@ -17458,7 +17453,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>451</v>
@@ -17580,7 +17575,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>452</v>
@@ -17702,13 +17697,13 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>22</v>
@@ -17826,7 +17821,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>434</v>
@@ -17944,7 +17939,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>435</v>
@@ -18064,7 +18059,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>436</v>
@@ -18186,7 +18181,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>437</v>
@@ -18234,7 +18229,7 @@
         <v>22</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>22</v>
@@ -18308,7 +18303,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>442</v>
@@ -18375,7 +18370,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>22</v>
@@ -18428,7 +18423,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>447</v>
@@ -18550,7 +18545,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>451</v>
@@ -18672,7 +18667,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>452</v>
@@ -18794,13 +18789,13 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>22</v>
@@ -18918,7 +18913,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>434</v>
@@ -19036,7 +19031,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>435</v>
@@ -19156,7 +19151,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>436</v>
@@ -19278,7 +19273,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>437</v>
@@ -19326,7 +19321,7 @@
         <v>22</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>22</v>
@@ -19400,7 +19395,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>442</v>
@@ -19467,7 +19462,7 @@
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>22</v>
@@ -19520,7 +19515,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>447</v>
@@ -19642,7 +19637,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>451</v>
@@ -19764,7 +19759,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>452</v>
@@ -19886,13 +19881,13 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>22</v>
@@ -20010,7 +20005,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>434</v>
@@ -20128,7 +20123,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>435</v>
@@ -20248,7 +20243,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>436</v>
@@ -20370,7 +20365,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>437</v>
@@ -20418,7 +20413,7 @@
         <v>22</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>22</v>
@@ -20492,7 +20487,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>442</v>
@@ -20559,7 +20554,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>22</v>
@@ -20612,7 +20607,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>447</v>
@@ -20734,7 +20729,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>451</v>
@@ -20856,7 +20851,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>452</v>
@@ -20978,13 +20973,13 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>425</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>22</v>
@@ -21102,7 +21097,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>434</v>
@@ -21220,7 +21215,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>435</v>
@@ -21340,7 +21335,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>436</v>
@@ -21462,7 +21457,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>437</v>
@@ -21510,7 +21505,7 @@
         <v>22</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>22</v>
@@ -21584,7 +21579,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>442</v>
@@ -21651,7 +21646,7 @@
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>22</v>
@@ -21704,7 +21699,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>447</v>
@@ -21826,7 +21821,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>451</v>
@@ -21948,7 +21943,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>452</v>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -675,9 +675,9 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;code value="698188003"/&gt;
-    &lt;display value="Chews betel quid"/&gt;
+    &lt;system value="https://twcore.mohw.gov.tw/ig/twha/CodeSystem/CS-BetelNutObservable"/&gt;
+    &lt;code value="betel-quid-chewing-status"/&gt;
+    &lt;display value="嚼檳榔狀態"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
+++ b/StructureDefinition-TWHA-SocialHistory-BetelNut.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
